--- a/MY CLASSES/RE-ASSESSMENTS/COTATION SHEET_L 3 NETWORKING AND INTERNET TECHNOLOGY-CPP.xlsx
+++ b/MY CLASSES/RE-ASSESSMENTS/COTATION SHEET_L 3 NETWORKING AND INTERNET TECHNOLOGY-CPP.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Landry\3D Objects\ETEFOP Trainer Docs\MY CLASSES\RE-ASSESSMENTS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Landry\3D Objects\ETEFOP Trainer Docs\ETEFOP-DOCS\MY CLASSES\RE-ASSESSMENTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -503,10 +503,10 @@
     <t xml:space="preserve"> MPAYIMANA CYIZA Landry</t>
   </si>
   <si>
-    <t>IOT SYSTEM INSTALLATON</t>
-  </si>
-  <si>
-    <t>NITIS301</t>
+    <t>C PROGRAMMING FUNDAMENTAKLS</t>
+  </si>
+  <si>
+    <t>GENCP302</t>
   </si>
 </sst>
 </file>
@@ -2565,7 +2565,9 @@
       <c r="K18" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="L18" s="25"/>
+      <c r="L18" s="25">
+        <v>20</v>
+      </c>
       <c r="M18" s="25"/>
       <c r="N18" s="25"/>
       <c r="O18" s="27" t="s">
